--- a/stories/arbres/TREE-DIF-004.xlsx
+++ b/stories/arbres/TREE-DIF-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est dans la cuisine, avec maman. Papa coupe le pain. Un camarade est là. Il parle peu. Jules le regarde. Maman dit : on peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Jules est dans la cuisine, avec maman. Papa coupe le pain. Un camarade est là. Il parle peu. Jules le regarde. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules est dans la cuisine, avec maman. Papa coupe le pain. Un camarade est là. Il parle peu. Jules le regarde.
+maman|On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1539,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules pose les cubes sur la table. Le camarade qui parle peu les regarde. Jules attend. Il tend un cube. Pas forcer la parole. Le camarade prend le cube. Maman dit : bien. On peut jouer ensemble.</t>
+          <t>Jules pose les cubes sur la table. Le camarade qui parle peu les regarde. Jules attend. Il tend un cube. Pas forcer la parole. Le camarade prend le cube. Bien. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1677,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose les cubes sur la table. Le camarade qui parle peu les regarde. Jules attend. Il tend un cube. Pas forcer la parole. Le camarade prend le cube.
+maman|Bien. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le camarade parle peu. On fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On attend. On tend un jouet. Jules respire. Papa est là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules tend un cube, puis une pomme. Le camarade qui parle peu choisit. Jules attend. Pas forcer la parole. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2581,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2748,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. Puis une pomme. Puis le chat. On dit merci. Jules ferme le sac. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2915,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3082,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules s'arrête près de le chien. une pomme est rangé. Un ballon s'immobilise. Jules essuie ses mains. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3249,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3416,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules se souvient de les cubes. Et de une pomme. Et de la poule. Le savon sent bon. Jules range encore un peu, près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3583,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3523,7 +3612,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Jules tend un cube, puis un yaourt. Le camarade touche le pot. Jules attend. Il tend un jouet. Papa dit : je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Jules tend un cube, puis un yaourt. Le camarade touche le pot. Jules attend. Il tend un jouet. Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3661,6 +3750,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules tend un cube, puis un yaourt. Le camarade touche le pot. Jules attend. Il tend un jouet.
+papa|Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3942,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4109,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après un yaourt. Près de les cubes. Jules s'arrête. Le sol est un peu froid. Jules marche près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4276,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4443,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules range un yaourt. le chien reste près de les cubes. Un vélo passe au loin. Jules ferme la porte, tout doux. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4610,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4519,7 +4639,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. un yaourt aussi. les cubes reste dans le souvenir. On souffle doucement. Jules s'assoit près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule est là. un yaourt aussi. les cubes reste dans le souvenir. On souffle doucement. Jules s'assoit près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4657,6 +4777,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. un yaourt aussi. les cubes reste dans le souvenir. On souffle doucement. Jules s'assoit près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4944,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5111,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules tend un cube, puis un morceau de pain. Le camarade le sent. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5302,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5469,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le chat. un morceau de pain est rangé. les cubes est fini. Une cloche tinte, tout loin. Jules répète tout bas le geste. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5636,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5803,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Jules pose un morceau de pain. les cubes est derrière. Une feuille tombe. Jules raccroche un linge. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5970,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5839,7 +5999,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Jules montre la poule. Papa a vu les cubes. Et un morceau de pain. Un ruban reste dans la poche. Jules dit : j'ai appris. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Jules montre la poule. Papa a vu les cubes. Et un morceau de pain. Un ruban reste dans la poche. J'ai appris. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5977,6 +6137,13 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules montre la poule. Papa a vu les cubes. Et un morceau de pain. Un ruban reste dans la poche.
+enfant-m|J'ai appris. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet.
+narrateur|Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6306,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6473,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Jules ouvre le livre. Le camarade qui parle peu touche une page. Jules attend. Il tend le livre. Pas forcer la parole. Le camarade sourit, sans parler. Papa coupe encore le pain. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6654,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On attend, ou on tend un jouet ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6827,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On attend. On tend un jouet. Jules retient le geste. Papa sourit. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7018,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6855,7 +7047,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Jules montre le livre, puis la pomme. Le camarade pointe. Jules attend. Il tend un jouet. Papa dit : je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Jules montre le livre, puis la pomme. Le camarade pointe. Jules attend. Il tend un jouet. Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -6993,6 +7185,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules montre le livre, puis la pomme. Le camarade pointe. Jules attend. Il tend un jouet.
+papa|Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7377,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7544,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. Puis une pomme. Puis le chat. Un galet est encore chaud. Maman n'est pas loin. Jules les rejoint. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7711,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7878,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules s'arrête près de le chien. une pomme est rangé. Il y a des miettes sur la table. Jules range le livre dans sa tête, comme un souvenir. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8045,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8212,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules se souvient de le livre. Et de une pomme. Et de la poule. Les chaussures font toc toc. Jules caresse le doudou. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8379,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8546,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules montre le livre, puis le yaourt. Le camarade reste silencieux. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8737,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8904,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après un yaourt. Près de le livre. Jules s'arrête. On rit un peu. Jules boit une gorgée d'eau. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9071,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9238,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules range un yaourt. le chien reste près de le livre. Une chaussette est encore sablée. Jules prend la main de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9405,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9171,7 +9434,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. un yaourt aussi. le livre reste dans le souvenir. La couverture est douce. Jules chuchote : c'est fini. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule est là. un yaourt aussi. le livre reste dans le souvenir. La couverture est douce. Jules chuchote : c'est fini. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9309,6 +9572,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. un yaourt aussi. le livre reste dans le souvenir. La couverture est douce. Jules chuchote : c'est fini. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9739,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9906,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules montre le livre, puis le pain. Le camarade sourit. Jules attend. Il tend un jouet. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10097,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10264,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le chat. un morceau de pain est rangé. le livre est fini. Un panier est posé sur le banc. Jules dit merci à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10431,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10598,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Jules pose un morceau de pain. le livre est derrière. L'eau coule, tout petit bruit. Jules souffle, puis sourit à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10765,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10932,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules montre la poule. Papa a vu le livre. Et un morceau de pain. Un crochet tient bien le manteau. Jules range la tasse. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11099,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11266,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Jules sort la dînette. Le camarade qui parle peu s'assoit. Jules attend. Il tend une tasse. Pas forcer la parole. Une tasse cliquette. Maman reste près d'eux. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11447,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On force la parole ?</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11620,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On attend. On tend un jouet. Jules hoche la tête. On continue, avec papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11811,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11978,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules tend une tasse, puis une pomme. Le camarade prend la tasse. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12169,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12336,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. Puis une pomme. Puis le chat. Le vent est doux. Jules plie un pull. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12503,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12670,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules s'arrête près de le chien. une pomme est rangé. On écoute jusqu'au bout. Jules sourit. Papa sourit aussi. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12837,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13004,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules se souvient de la dînette. Et de une pomme. Et de la poule. Un linge sèche à l'air. Jules enfile ses chaussons. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13171,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13338,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules tend une tasse, puis un yaourt. Le camarade tapote. Jules attend. Il tend un jouet. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13529,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13696,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après un yaourt. Près de la dînette. Jules s'arrête. On se tient la main. Jules montre le chat à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13863,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14030,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules range un yaourt. le chien reste près de la dînette. On entend un oiseau. Jules pose un yaourt à sa place. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14197,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13823,7 +14226,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. un yaourt aussi. la dînette reste dans le souvenir. La lumière est claire. Jules serre la main de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule est là. un yaourt aussi. la dînette reste dans le souvenir. La lumière est claire. Jules serre la main de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13961,6 +14364,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. un yaourt aussi. la dînette reste dans le souvenir. La lumière est claire. Jules serre la main de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14531,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14147,7 +14560,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Jules tend une tasse, puis le pain. Le camarade s'assoit. Jules attend. Pas forcer la parole. Papa dit : je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Jules tend une tasse, puis le pain. Le camarade s'assoit. Jules attend. Pas forcer la parole. Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14285,6 +14698,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules tend une tasse, puis le pain. Le camarade s'assoit. Jules attend. Pas forcer la parole.
+papa|Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14890,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15057,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le chat. un morceau de pain est rangé. la dînette est fini. Une tasse cliquette. Jules écoute papa encore une fois. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15224,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15391,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Jules pose un morceau de pain. la dînette est derrière. Un chat miaule une fois. Jules tend le chien à maman. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15558,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15725,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules montre la poule. Papa a vu la dînette. Et un morceau de pain. Ça sent le pain chaud. Jules pose sa tête un moment. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15892,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15932,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-004.xlsx
+++ b/stories/arbres/TREE-DIF-004.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 maman|On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
 maman|Bien. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|Le camarade parle peu. On fait quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Oui. On attend. On tend un jouet. Jules respire. Papa est là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2238,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
           <t>narrateur|Jules tend un cube, puis une pomme. Le camarade qui parle peu choisit. Jules attend. Pas forcer la parole. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2584,6 +2596,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2753,6 +2770,7 @@
           <t>narrateur|Jules a choisi les cubes. Puis une pomme. Puis le chat. On dit merci. Jules ferme le sac. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2920,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3087,6 +3106,11 @@
           <t>narrateur|Jules s'arrête près de le chien. une pomme est rangé. Un ballon s'immobilise. Jules essuie ses mains. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3254,6 +3278,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3421,6 +3446,7 @@
           <t>narrateur|Jules se souvient de les cubes. Et de une pomme. Et de la poule. Le savon sent bon. Jules range encore un peu, près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3588,6 +3614,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3756,6 +3783,7 @@
 papa|Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3973,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4114,6 +4147,7 @@
           <t>narrateur|Avec le chat. Après un yaourt. Près de les cubes. Jules s'arrête. Le sol est un peu froid. Jules marche près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4281,6 +4315,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4448,6 +4483,11 @@
           <t>narrateur|Jules range un yaourt. le chien reste près de les cubes. Un vélo passe au loin. Jules ferme la porte, tout doux. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4615,6 +4655,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4782,6 +4823,7 @@
           <t>narrateur|La poule est là. un yaourt aussi. les cubes reste dans le souvenir. On souffle doucement. Jules s'assoit près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4949,6 +4991,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5116,6 +5159,7 @@
           <t>narrateur|Jules tend un cube, puis un morceau de pain. Le camarade le sent. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5349,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5474,6 +5523,7 @@
           <t>narrateur|Jules rejoint le chat. un morceau de pain est rangé. les cubes est fini. Une cloche tinte, tout loin. Jules répète tout bas le geste. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5641,6 +5691,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5808,6 +5859,11 @@
           <t>narrateur|Près de le chien. Jules pose un morceau de pain. les cubes est derrière. Une feuille tombe. Jules raccroche un linge. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5975,6 +6031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6201,7 @@
 narrateur|Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6369,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6478,6 +6537,7 @@
           <t>narrateur|Jules ouvre le livre. Le camarade qui parle peu touche une page. Jules attend. Il tend le livre. Pas forcer la parole. Le camarade sourit, sans parler. Papa coupe encore le pain. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6661,6 +6721,7 @@
           <t>narrateur|On attend, ou on tend un jouet ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6832,6 +6893,7 @@
           <t>narrateur|Oui. On attend. On tend un jouet. Jules retient le geste. Papa sourit. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7023,6 +7085,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7191,6 +7254,7 @@
 papa|Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7380,6 +7444,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7549,6 +7618,7 @@
           <t>narrateur|Jules a choisi le livre. Puis une pomme. Puis le chat. Un galet est encore chaud. Maman n'est pas loin. Jules les rejoint. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7716,6 +7786,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7883,6 +7954,11 @@
           <t>narrateur|Jules s'arrête près de le chien. une pomme est rangé. Il y a des miettes sur la table. Jules range le livre dans sa tête, comme un souvenir. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8050,6 +8126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8217,6 +8294,7 @@
           <t>narrateur|Jules se souvient de le livre. Et de une pomme. Et de la poule. Les chaussures font toc toc. Jules caresse le doudou. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8384,6 +8462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8551,6 +8630,7 @@
           <t>narrateur|Jules montre le livre, puis le yaourt. Le camarade reste silencieux. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8740,6 +8820,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8909,6 +8994,7 @@
           <t>narrateur|Avec le chat. Après un yaourt. Près de le livre. Jules s'arrête. On rit un peu. Jules boit une gorgée d'eau. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9076,6 +9162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9243,6 +9330,11 @@
           <t>narrateur|Jules range un yaourt. le chien reste près de le livre. Une chaussette est encore sablée. Jules prend la main de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9410,6 +9502,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9577,6 +9670,7 @@
           <t>narrateur|La poule est là. un yaourt aussi. le livre reste dans le souvenir. La couverture est douce. Jules chuchote : c'est fini. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9744,6 +9838,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9911,6 +10006,7 @@
           <t>narrateur|Jules montre le livre, puis le pain. Le camarade sourit. Jules attend. Il tend un jouet. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10100,6 +10196,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10269,6 +10370,7 @@
           <t>narrateur|Jules rejoint le chat. un morceau de pain est rangé. le livre est fini. Un panier est posé sur le banc. Jules dit merci à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10436,6 +10538,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10603,6 +10706,11 @@
           <t>narrateur|Près de le chien. Jules pose un morceau de pain. le livre est derrière. L'eau coule, tout petit bruit. Jules souffle, puis sourit à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10770,6 +10878,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10937,6 +11046,7 @@
           <t>narrateur|Jules montre la poule. Papa a vu le livre. Et un morceau de pain. Un crochet tient bien le manteau. Jules range la tasse. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11104,6 +11214,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11271,6 +11382,7 @@
           <t>narrateur|Jules sort la dînette. Le camarade qui parle peu s'assoit. Jules attend. Il tend une tasse. Pas forcer la parole. Une tasse cliquette. Maman reste près d'eux. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11454,6 +11566,7 @@
           <t>narrateur|On force la parole ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11625,6 +11738,7 @@
           <t>narrateur|Oui. On attend. On tend un jouet. Jules hoche la tête. On continue, avec papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11816,6 +11930,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11983,6 +12098,7 @@
           <t>narrateur|Jules tend une tasse, puis une pomme. Le camarade prend la tasse. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12172,6 +12288,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12341,6 +12462,7 @@
           <t>narrateur|Jules a choisi la dînette. Puis une pomme. Puis le chat. Le vent est doux. Jules plie un pull. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12508,6 +12630,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12675,6 +12798,11 @@
           <t>narrateur|Jules s'arrête près de le chien. une pomme est rangé. On écoute jusqu'au bout. Jules sourit. Papa sourit aussi. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12842,6 +12970,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13009,6 +13138,7 @@
           <t>narrateur|Jules se souvient de la dînette. Et de une pomme. Et de la poule. Un linge sèche à l'air. Jules enfile ses chaussons. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13176,6 +13306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13343,6 +13474,7 @@
           <t>narrateur|Jules tend une tasse, puis un yaourt. Le camarade tapote. Jules attend. Il tend un jouet. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13532,6 +13664,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13701,6 +13838,7 @@
           <t>narrateur|Avec le chat. Après un yaourt. Près de la dînette. Jules s'arrête. On se tient la main. Jules montre le chat à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13868,6 +14006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14035,6 +14174,11 @@
           <t>narrateur|Jules range un yaourt. le chien reste près de la dînette. On entend un oiseau. Jules pose un yaourt à sa place. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14202,6 +14346,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14369,6 +14514,7 @@
           <t>narrateur|La poule est là. un yaourt aussi. la dînette reste dans le souvenir. La lumière est claire. Jules serre la main de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14536,6 +14682,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14704,6 +14851,7 @@
 papa|Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14893,6 +15041,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15062,6 +15215,7 @@
           <t>narrateur|Jules rejoint le chat. un morceau de pain est rangé. la dînette est fini. Une tasse cliquette. Jules écoute papa encore une fois. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15229,6 +15383,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15396,6 +15551,11 @@
           <t>narrateur|Près de le chien. Jules pose un morceau de pain. la dînette est derrière. Un chat miaule une fois. Jules tend le chien à maman. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15563,6 +15723,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15730,6 +15891,7 @@
           <t>narrateur|Jules montre la poule. Papa a vu la dînette. Et un morceau de pain. Ça sent le pain chaud. Jules pose sa tête un moment. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15897,6 +16059,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15915,7 +16078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15939,6 +16102,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15953,7 +16130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16140,6 +16317,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-004.xlsx
+++ b/stories/arbres/TREE-DIF-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Un camarade qui parle peu — dans la cuisine</t>
+          <t>La gouttière et le cube de Nino</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DIF.COR.001</t>
+          <t>DIF.BES.002</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La gouttière chante sur le zinc. Nino arrive, tout calme, et parle peu. Raphaël attend, tend un cube, une tasse, une pomme. Ils jouent ensemble, avec peu de mots.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est dans la cuisine, avec maman. Papa coupe le pain. Un camarade est là. Il parle peu. Jules le regarde. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>La gouttière fait un chant, tout fin. Des gouttes tapent le zinc, une par une. La buée recouvre la vitre de la cuisine. Derrière, le village est tout flou. La nappe à carreaux sent le savon. Une miette de pain dort près du saladier. La soupe fume dans la casserole. La cuillère en bois goutte, tout lentement. Papa coupe le pain, tout près du bord. Maman essuie la buée d'un coin de torchon. Tu entends la gouttière, Raphaël ? Elle fait ploc, papa. La soupe est presque prête. Des chaussures mouillées attendent près de la porte. Une écharpe goutte encore, sur le carrelage. En ce moment, Nino pousse la porte. Nino parle peu. Il regarde le carrelage, tout calme. Raphaël a envie de demander plein de choses. Il respire, tout doux. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On n'imite pas. On peut jouer ensemble. Nino pose son sac, sans un mot. J'attends. Tu attends, c'est bien. Une goutte glisse encore sur le zinc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,8 +1337,35 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules est dans la cuisine, avec maman. Papa coupe le pain. Un camarade est là. Il parle peu. Jules le regarde.
-maman|On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>narrateur|La gouttière fait un chant, tout fin.
+narrateur|Des gouttes tapent le zinc, une par une.
+narrateur|La buée recouvre la vitre de la cuisine.
+narrateur|Derrière, le village est tout flou.
+narrateur|La nappe à carreaux sent le savon.
+narrateur|Une miette de pain dort près du saladier.
+narrateur|La soupe fume dans la casserole.
+narrateur|La cuillère en bois goutte, tout lentement.
+narrateur|Papa coupe le pain, tout près du bord.
+narrateur|Maman essuie la buée d'un coin de torchon.
+papa|Tu entends la gouttière, Raphaël ?
+enfant-m|Elle fait ploc, papa.
+maman|La soupe est presque prête.
+narrateur|Des chaussures mouillées attendent près de la porte.
+narrateur|Une écharpe goutte encore, sur le carrelage.
+narrateur|En ce moment, Nino pousse la porte.
+narrateur|Nino parle peu.
+narrateur|Il regarde le carrelage, tout calme.
+narrateur|Raphaël a envie de demander plein de choses.
+narrateur|Il respire, tout doux.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+papa|On n'imite pas.
+papa|On peut jouer ensemble.
+narrateur|Nino pose son sac, sans un mot.
+enfant-m|J'attends.
+maman|Tu attends, c'est bien.
+narrateur|Une goutte glisse encore sur le zinc.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1354,7 +1393,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent sur le bas de l'armoire. Les cubes, le livre, ou la dînette ? On peut tendre un jouet. On peut attendre.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1557,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent sur le bas de l'armoire.
+papa|Les cubes, le livre, ou la dînette ?
+maman|On peut tendre un jouet.
+maman|On peut attendre.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules pose les cubes sur la table. Le camarade qui parle peu les regarde. Jules attend. Il tend un cube. Pas forcer la parole. Le camarade prend le cube. Bien. On peut jouer ensemble.</t>
+          <t>Raphaël pose les cubes sur la table. Un cube rouge sent le pin. Un cube bleu fait clic, tout doux. Nino les regarde, sans un mot. Ses mains restent sur ses genoux. Raphaël a envie de demander. Il attend, tout calme. Je lui tends le cube rouge. Nino prend le cube. Il le pose, tout droit. Bravo, Raphaël. Tu as su attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Deux cubes font une petite tour. Nino ajoute le cube bleu. La tour tient, tout silencieuse.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,8 +1728,24 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules pose les cubes sur la table. Le camarade qui parle peu les regarde. Jules attend. Il tend un cube. Pas forcer la parole. Le camarade prend le cube.
-maman|Bien. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël pose les cubes sur la table.
+narrateur|Un cube rouge sent le pin.
+narrateur|Un cube bleu fait clic, tout doux.
+narrateur|Nino les regarde, sans un mot.
+narrateur|Ses mains restent sur ses genoux.
+narrateur|Raphaël a envie de demander.
+narrateur|Il attend, tout calme.
+enfant-m|Je lui tends le cube rouge.
+narrateur|Nino prend le cube.
+narrateur|Il le pose, tout droit.
+maman|Bravo, Raphaël.
+maman|Tu as su attendre.
+papa|On peut tendre un jouet.
+papa|On ne force pas la parole.
+papa|On peut jouer ensemble.
+narrateur|Deux cubes font une petite tour.
+narrateur|Nino ajoute le cube bleu.
+narrateur|La tour tient, tout silencieuse.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1715,7 +1773,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le camarade parle peu. On fait quoi ?</t>
+          <t>Nino parle peu. On fait quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1871,7 +1929,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le camarade parle peu. On fait quoi ?</t>
+          <t>narrateur|Nino parle peu.
+maman|On fait quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1899,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On attend. On tend un jouet. Jules respire. Papa est là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Oui. On attend. On tend un jouet. Raphaël souffle un peu. Le cube rouge reste dans la main de Nino. J'ai attendu. Bravo, Raphaël. C'est du bon travail. On ne force pas la parole. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2043,7 +2102,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On attend. On tend un jouet. Jules respire. Papa est là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On attend.
+papa|On tend un jouet.
+narrateur|Raphaël souffle un peu.
+narrateur|Le cube rouge reste dans la main de Nino.
+enfant-m|J'ai attendu.
+maman|Bravo, Raphaël.
+maman|C'est du bon travail.
+papa|On ne force pas la parole.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2071,7 +2139,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>Trois goûters attendent, tout proches. Une pomme, un yaourt, ou un morceau de pain ? On tend. On attend.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2235,7 +2303,9 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|Trois goûters attendent, tout proches.
+maman|Une pomme, un yaourt, ou un morceau de pain ?
+papa|On tend. On attend.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2263,7 +2333,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Jules tend un cube, puis une pomme. Le camarade qui parle peu choisit. Jules attend. Pas forcer la parole. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Papa coupe une pomme jaune. La peau est lisse, un peu froide. Une goutte de jus brille sur la table. Tu veux un quartier, Nino ? Nino regarde la pomme. Il ne dit rien. Raphaël attend. Je lui tends le quartier. Nino prend la pomme. Il croque, tout petit. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. Un cube attrape un reflet de pomme. On a encore les cubes, sur la table. On peut attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2403,7 +2473,26 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Jules tend un cube, puis une pomme. Le camarade qui parle peu choisit. Jules attend. Pas forcer la parole. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>narrateur|Papa coupe une pomme jaune.
+narrateur|La peau est lisse, un peu froide.
+narrateur|Une goutte de jus brille sur la table.
+papa|Tu veux un quartier, Nino ?
+narrateur|Nino regarde la pomme.
+narrateur|Il ne dit rien.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le quartier.
+narrateur|Nino prend la pomme.
+narrateur|Il croque, tout petit.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+papa|On peut jouer ensemble.
+maman|Bravo, Raphaël.
+maman|Tu as tendu, sans presser.
+narrateur|Un cube attrape un reflet de pomme.
+narrateur|On a encore les cubes, sur la table.
+maman|On peut attendre.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2431,7 +2520,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Un animal de la maison attend, tout près. Le chat, le chien, ou la poule ? On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2595,7 +2684,9 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Un animal de la maison attend, tout près.
+papa|Le chat, le chien, ou la poule ?
+maman|On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2627,7 +2718,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi les cubes. Puis une pomme. Puis le chat. On dit merci. Jules ferme le sac. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chat de la maison s'étire sur la chaise. Son dos est chaud, tout soyeux. Il fait un petit ronron. Le chat aime le calme, lui aussi. Nino tend un doigt, tout lentement. Raphaël attend. Je lui tends le jouet souris. Nino pose le jouet près du chat. On peut attendre. On peut tendre un jouet. On ne force pas la parole. Bravo, Raphaël. Tu as su attendre. Un cube rouge reste près des moustaches. Raphaël a encore les cubes. Il reste un quartier de pomme. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2767,7 +2858,27 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi les cubes. Puis une pomme. Puis le chat. On dit merci. Jules ferme le sac. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat de la maison s'étire sur la chaise.
+narrateur|Son dos est chaud, tout soyeux.
+narrateur|Il fait un petit ronron.
+maman|Le chat aime le calme, lui aussi.
+narrateur|Nino tend un doigt, tout lentement.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le jouet souris.
+narrateur|Nino pose le jouet près du chat.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+papa|Bravo, Raphaël.
+papa|Tu as su attendre.
+narrateur|Un cube rouge reste près des moustaches.
+narrateur|Raphaël a encore les cubes.
+narrateur|Il reste un quartier de pomme.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2795,7 +2906,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec les cubes. Nino a pris la pomme, sans parler. Ils ont vu le chat, tout ensemble. Le chat se rendort, tout rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2935,7 +3046,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec les cubes.
+narrateur|Nino a pris la pomme, sans parler.
+narrateur|Ils ont vu le chat, tout ensemble.
+narrateur|Le chat se rendort, tout rond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2963,7 +3083,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Jules s'arrête près de le chien. une pomme est rangé. Un ballon s'immobilise. Jules essuie ses mains. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chien gratte doucement la porte. Ses poils sentent l'herbe mouillée. Il fait un wouaf, tout amical. Le chien est content, tout simplement. Nino recule un peu, puis avance. Raphaël attend, tout près. Je lui tends la balle molle. Nino pose la balle au sol. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. C'est du bon travail. Un cube roule jusqu'aux pattes mouillées. Raphaël a encore les cubes. Il reste un quartier de pomme. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3103,7 +3223,28 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Jules s'arrête près de le chien. une pomme est rangé. Un ballon s'immobilise. Jules essuie ses mains. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien gratte doucement la porte.
+narrateur|Ses poils sentent l'herbe mouillée.
+narrateur|Il fait un wouaf, tout amical.
+papa|Le chien est content, tout simplement.
+narrateur|Nino recule un peu, puis avance.
+narrateur|Raphaël attend, tout près.
+enfant-m|Je lui tends la balle molle.
+narrateur|Nino pose la balle au sol.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Un cube roule jusqu'aux pattes mouillées.
+narrateur|Raphaël a encore les cubes.
+narrateur|Il reste un quartier de pomme.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3135,7 +3276,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec les cubes. Nino a pris la pomme, sans parler. Ils ont vu le chien, tout ensemble. Le chien pose la tête, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3275,7 +3416,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec les cubes.
+narrateur|Nino a pris la pomme, sans parler.
+narrateur|Ils ont vu le chien, tout ensemble.
+narrateur|Le chien pose la tête, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3303,7 +3453,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Jules se souvient de les cubes. Et de une pomme. Et de la poule. Le savon sent bon. Jules range encore un peu, près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule picore près du bac, dehors. Ses plumes sont rousses, un peu mouillées. Elle fait cot cot, tout bas. On la regarde, tout doux. Nino s'accroupit, sans un mot. Raphaël attend à côté. Je lui tends le seau de grains. Nino pose le seau, tout lentement. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. Un cube jaune brille près des grains. Raphaël a encore les cubes. Il reste un quartier de pomme. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3443,7 +3593,28 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Jules se souvient de les cubes. Et de une pomme. Et de la poule. Le savon sent bon. Jules range encore un peu, près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près du bac, dehors.
+narrateur|Ses plumes sont rousses, un peu mouillées.
+narrateur|Elle fait cot cot, tout bas.
+maman|On la regarde, tout doux.
+narrateur|Nino s'accroupit, sans un mot.
+narrateur|Raphaël attend à côté.
+enfant-m|Je lui tends le seau de grains.
+narrateur|Nino pose le seau, tout lentement.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo, Raphaël.
+papa|Tu as tendu, sans presser.
+narrateur|Un cube jaune brille près des grains.
+narrateur|Raphaël a encore les cubes.
+narrateur|Il reste un quartier de pomme.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3471,7 +3642,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec les cubes. Nino a pris la pomme, sans parler. Ils ont vu la poule, tout ensemble. La poule rentre sous l'auvent, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3611,7 +3782,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec les cubes.
+narrateur|Nino a pris la pomme, sans parler.
+narrateur|Ils ont vu la poule, tout ensemble.
+narrateur|La poule rentre sous l'auvent, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3639,7 +3819,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Jules tend un cube, puis un yaourt. Le camarade touche le pot. Jules attend. Il tend un jouet. Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Maman sort un yaourt du saladier froid. Le pot est lisse, un peu mouillé. Une cuillère tape le bord. Le yaourt est là, Nino. Nino tapote le pot. Raphaël attend, les mains sages. Je lui tends la cuillère. Nino prend la cuillère. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. Tu as su attendre. Une goutte blanche reste sur la nappe. Un cube blanc colle un peu de yaourt. On a encore les cubes, sur la table. On peut attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3779,8 +3959,25 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Jules tend un cube, puis un yaourt. Le camarade touche le pot. Jules attend. Il tend un jouet.
-papa|Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>narrateur|Maman sort un yaourt du saladier froid.
+narrateur|Le pot est lisse, un peu mouillé.
+narrateur|Une cuillère tape le bord.
+maman|Le yaourt est là, Nino.
+narrateur|Nino tapote le pot.
+narrateur|Raphaël attend, les mains sages.
+enfant-m|Je lui tends la cuillère.
+narrateur|Nino prend la cuillère.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Tu as su attendre.
+narrateur|Une goutte blanche reste sur la nappe.
+narrateur|Un cube blanc colle un peu de yaourt.
+narrateur|On a encore les cubes, sur la table.
+maman|On peut attendre.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3808,7 +4005,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Un animal de la maison attend, tout près. Le chat, le chien, ou la poule ? On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3972,7 +4169,9 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Un animal de la maison attend, tout près.
+papa|Le chat, le chien, ou la poule ?
+maman|On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -4004,7 +4203,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec le chat. Après un yaourt. Près de les cubes. Jules s'arrête. Le sol est un peu froid. Jules marche près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chat de la maison s'étire sur la chaise. Son dos est chaud, tout soyeux. Il fait un petit ronron. Le chat aime le calme, lui aussi. Nino tend un doigt, tout lentement. Raphaël attend. Je lui tends le jouet souris. Nino pose le jouet près du chat. On peut attendre. On peut tendre un jouet. On ne force pas la parole. Bravo, Raphaël. Tu as su attendre. Le chat ignore le pot, tout fier. Raphaël a encore les cubes. Il reste un peu de yaourt. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4144,7 +4343,27 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec le chat. Après un yaourt. Près de les cubes. Jules s'arrête. Le sol est un peu froid. Jules marche près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat de la maison s'étire sur la chaise.
+narrateur|Son dos est chaud, tout soyeux.
+narrateur|Il fait un petit ronron.
+maman|Le chat aime le calme, lui aussi.
+narrateur|Nino tend un doigt, tout lentement.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le jouet souris.
+narrateur|Nino pose le jouet près du chat.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+papa|Bravo, Raphaël.
+papa|Tu as su attendre.
+narrateur|Le chat ignore le pot, tout fier.
+narrateur|Raphaël a encore les cubes.
+narrateur|Il reste un peu de yaourt.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4172,7 +4391,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec les cubes. Nino a pris le yaourt, sans parler. Ils ont vu le chat, tout ensemble. Le chat se rendort, tout rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4312,7 +4531,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec les cubes.
+narrateur|Nino a pris le yaourt, sans parler.
+narrateur|Ils ont vu le chat, tout ensemble.
+narrateur|Le chat se rendort, tout rond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4340,7 +4568,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Jules range un yaourt. le chien reste près de les cubes. Un vélo passe au loin. Jules ferme la porte, tout doux. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chien gratte doucement la porte. Ses poils sentent l'herbe mouillée. Il fait un wouaf, tout amical. Le chien est content, tout simplement. Nino recule un peu, puis avance. Raphaël attend, tout près. Je lui tends la balle molle. Nino pose la balle au sol. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. C'est du bon travail. Le chien renifle le pot, puis s'assoit. Raphaël a encore les cubes. Il reste un peu de yaourt. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4480,7 +4708,28 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Jules range un yaourt. le chien reste près de les cubes. Un vélo passe au loin. Jules ferme la porte, tout doux. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien gratte doucement la porte.
+narrateur|Ses poils sentent l'herbe mouillée.
+narrateur|Il fait un wouaf, tout amical.
+papa|Le chien est content, tout simplement.
+narrateur|Nino recule un peu, puis avance.
+narrateur|Raphaël attend, tout près.
+enfant-m|Je lui tends la balle molle.
+narrateur|Nino pose la balle au sol.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le chien renifle le pot, puis s'assoit.
+narrateur|Raphaël a encore les cubes.
+narrateur|Il reste un peu de yaourt.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -4512,7 +4761,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec les cubes. Nino a pris le yaourt, sans parler. Ils ont vu le chien, tout ensemble. Le chien pose la tête, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4652,7 +4901,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec les cubes.
+narrateur|Nino a pris le yaourt, sans parler.
+narrateur|Ils ont vu le chien, tout ensemble.
+narrateur|Le chien pose la tête, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4680,7 +4938,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>La poule est là. un yaourt aussi. les cubes reste dans le souvenir. On souffle doucement. Jules s'assoit près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule picore près du bac, dehors. Ses plumes sont rousses, un peu mouillées. Elle fait cot cot, tout bas. On la regarde, tout doux. Nino s'accroupit, sans un mot. Raphaël attend à côté. Je lui tends le seau de grains. Nino pose le seau, tout lentement. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. La poule picore loin du yaourt froid. Raphaël a encore les cubes. Il reste un peu de yaourt. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4820,7 +5078,28 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|La poule est là. un yaourt aussi. les cubes reste dans le souvenir. On souffle doucement. Jules s'assoit près de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près du bac, dehors.
+narrateur|Ses plumes sont rousses, un peu mouillées.
+narrateur|Elle fait cot cot, tout bas.
+maman|On la regarde, tout doux.
+narrateur|Nino s'accroupit, sans un mot.
+narrateur|Raphaël attend à côté.
+enfant-m|Je lui tends le seau de grains.
+narrateur|Nino pose le seau, tout lentement.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo, Raphaël.
+papa|Tu as tendu, sans presser.
+narrateur|La poule picore loin du yaourt froid.
+narrateur|Raphaël a encore les cubes.
+narrateur|Il reste un peu de yaourt.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4848,7 +5127,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec les cubes. Nino a pris le yaourt, sans parler. Ils ont vu la poule, tout ensemble. La poule rentre sous l'auvent, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4988,7 +5267,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec les cubes.
+narrateur|Nino a pris le yaourt, sans parler.
+narrateur|Ils ont vu la poule, tout ensemble.
+narrateur|La poule rentre sous l'auvent, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5016,7 +5304,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Jules tend un cube, puis un morceau de pain. Le camarade le sent. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Papa tend un morceau de pain. La croûte est encore tiède. Ça sent le four, tout doux. Tu le sens, Nino ? Nino approche le pain. Il ne parle pas. Raphaël attend la fin du silence. Je lui tends le pain. Nino prend le morceau. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Une miette reste près du cube. Une miette de pain dort près d'un cube. On a encore les cubes, sur la table. On peut attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5156,7 +5444,25 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Jules tend un cube, puis un morceau de pain. Le camarade le sent. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>narrateur|Papa tend un morceau de pain.
+narrateur|La croûte est encore tiède.
+narrateur|Ça sent le four, tout doux.
+papa|Tu le sens, Nino ?
+narrateur|Nino approche le pain.
+narrateur|Il ne parle pas.
+narrateur|Raphaël attend la fin du silence.
+enfant-m|Je lui tends le pain.
+narrateur|Nino prend le morceau.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+papa|On peut jouer ensemble.
+maman|Bravo, Raphaël.
+narrateur|Une miette reste près du cube.
+narrateur|Une miette de pain dort près d'un cube.
+narrateur|On a encore les cubes, sur la table.
+maman|On peut attendre.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5184,7 +5490,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Un animal de la maison attend, tout près. Le chat, le chien, ou la poule ? On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5348,7 +5654,9 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Un animal de la maison attend, tout près.
+papa|Le chat, le chien, ou la poule ?
+maman|On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -5380,7 +5688,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le chat. un morceau de pain est rangé. les cubes est fini. Une cloche tinte, tout loin. Jules répète tout bas le geste. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chat de la maison s'étire sur la chaise. Son dos est chaud, tout soyeux. Il fait un petit ronron. Le chat aime le calme, lui aussi. Nino tend un doigt, tout lentement. Raphaël attend. Je lui tends le jouet souris. Nino pose le jouet près du chat. On peut attendre. On peut tendre un jouet. On ne force pas la parole. Bravo, Raphaël. Tu as su attendre. Une miette intéresse le chat, une seconde. Raphaël a encore les cubes. Il reste une croûte de pain. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5520,7 +5828,27 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le chat. un morceau de pain est rangé. les cubes est fini. Une cloche tinte, tout loin. Jules répète tout bas le geste. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat de la maison s'étire sur la chaise.
+narrateur|Son dos est chaud, tout soyeux.
+narrateur|Il fait un petit ronron.
+maman|Le chat aime le calme, lui aussi.
+narrateur|Nino tend un doigt, tout lentement.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le jouet souris.
+narrateur|Nino pose le jouet près du chat.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+papa|Bravo, Raphaël.
+papa|Tu as su attendre.
+narrateur|Une miette intéresse le chat, une seconde.
+narrateur|Raphaël a encore les cubes.
+narrateur|Il reste une croûte de pain.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5548,7 +5876,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec les cubes. Nino a pris le pain, sans parler. Ils ont vu le chat, tout ensemble. Le chat se rendort, tout rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5688,7 +6016,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec les cubes.
+narrateur|Nino a pris le pain, sans parler.
+narrateur|Ils ont vu le chat, tout ensemble.
+narrateur|Le chat se rendort, tout rond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5716,7 +6053,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de le chien. Jules pose un morceau de pain. les cubes est derrière. Une feuille tombe. Jules raccroche un linge. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chien gratte doucement la porte. Ses poils sentent l'herbe mouillée. Il fait un wouaf, tout amical. Le chien est content, tout simplement. Nino recule un peu, puis avance. Raphaël attend, tout près. Je lui tends la balle molle. Nino pose la balle au sol. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. C'est du bon travail. Le chien pose le nez près du pain. Raphaël a encore les cubes. Il reste une croûte de pain. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5856,7 +6193,28 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de le chien. Jules pose un morceau de pain. les cubes est derrière. Une feuille tombe. Jules raccroche un linge. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien gratte doucement la porte.
+narrateur|Ses poils sentent l'herbe mouillée.
+narrateur|Il fait un wouaf, tout amical.
+papa|Le chien est content, tout simplement.
+narrateur|Nino recule un peu, puis avance.
+narrateur|Raphaël attend, tout près.
+enfant-m|Je lui tends la balle molle.
+narrateur|Nino pose la balle au sol.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le chien pose le nez près du pain.
+narrateur|Raphaël a encore les cubes.
+narrateur|Il reste une croûte de pain.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -5888,7 +6246,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec les cubes. Nino a pris le pain, sans parler. Ils ont vu le chien, tout ensemble. Le chien pose la tête, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6028,7 +6386,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec les cubes.
+narrateur|Nino a pris le pain, sans parler.
+narrateur|Ils ont vu le chien, tout ensemble.
+narrateur|Le chien pose la tête, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6056,7 +6423,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Jules montre la poule. Papa a vu les cubes. Et un morceau de pain. Un ruban reste dans la poche. J'ai appris. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule picore près du bac, dehors. Ses plumes sont rousses, un peu mouillées. Elle fait cot cot, tout bas. On la regarde, tout doux. Nino s'accroupit, sans un mot. Raphaël attend à côté. Je lui tends le seau de grains. Nino pose le seau, tout lentement. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. La poule préfère le grain au pain. Raphaël a encore les cubes. Il reste une croûte de pain. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6196,9 +6563,28 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Jules montre la poule. Papa a vu les cubes. Et un morceau de pain. Un ruban reste dans la poche.
-enfant-m|J'ai appris. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet.
-narrateur|Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près du bac, dehors.
+narrateur|Ses plumes sont rousses, un peu mouillées.
+narrateur|Elle fait cot cot, tout bas.
+maman|On la regarde, tout doux.
+narrateur|Nino s'accroupit, sans un mot.
+narrateur|Raphaël attend à côté.
+enfant-m|Je lui tends le seau de grains.
+narrateur|Nino pose le seau, tout lentement.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo, Raphaël.
+papa|Tu as tendu, sans presser.
+narrateur|La poule préfère le grain au pain.
+narrateur|Raphaël a encore les cubes.
+narrateur|Il reste une croûte de pain.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6226,7 +6612,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec les cubes. Nino a pris le pain, sans parler. Ils ont vu la poule, tout ensemble. La poule rentre sous l'auvent, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6366,7 +6752,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec les cubes.
+narrateur|Nino a pris le pain, sans parler.
+narrateur|Ils ont vu la poule, tout ensemble.
+narrateur|La poule rentre sous l'auvent, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6394,7 +6789,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules ouvre le livre. Le camarade qui parle peu touche une page. Jules attend. Il tend le livre. Pas forcer la parole. Le camarade sourit, sans parler. Papa coupe encore le pain. On peut jouer ensemble.</t>
+          <t>Raphaël ouvre le livre à images. La page sent le papier, un peu sec. Un chat dessiné lève la patte. Nino touche le bord de la page. Il ne dit rien. Raphaël attend, les mains à plat. Je lui tends le livre. Nino prend le livre. Il caresse l'image, tout lentement. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Une page tourne, tout seule presque. J'attends encore. Bravo. C'est du bon travail. Nino sourit, sans parler.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6534,7 +6929,24 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Jules ouvre le livre. Le camarade qui parle peu touche une page. Jules attend. Il tend le livre. Pas forcer la parole. Le camarade sourit, sans parler. Papa coupe encore le pain. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël ouvre le livre à images.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Un chat dessiné lève la patte.
+narrateur|Nino touche le bord de la page.
+narrateur|Il ne dit rien.
+narrateur|Raphaël attend, les mains à plat.
+enfant-m|Je lui tends le livre.
+narrateur|Nino prend le livre.
+narrateur|Il caresse l'image, tout lentement.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+narrateur|Une page tourne, tout seule presque.
+enfant-m|J'attends encore.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nino sourit, sans parler.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6562,7 +6974,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>On attend, ou on tend un jouet ?</t>
+          <t>Nino touche la page. On attend, ou on tend un jouet ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6718,7 +7130,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|On attend, ou on tend un jouet ?</t>
+          <t>narrateur|Nino touche la page.
+papa|On attend, ou on tend un jouet ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6746,7 +7159,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On attend. On tend un jouet. Jules retient le geste. Papa sourit. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Oui. On attend. On tend un jouet. La page reste ouverte, tout calme. Je tends le livre. Bravo. Tu as su attendre. On ne force pas la parole. Nino caresse encore le chat dessiné.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6890,7 +7303,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On attend. On tend un jouet. Jules retient le geste. Papa sourit. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>maman|Oui.
+maman|On attend.
+maman|On tend un jouet.
+narrateur|La page reste ouverte, tout calme.
+enfant-m|Je tends le livre.
+papa|Bravo.
+papa|Tu as su attendre.
+maman|On ne force pas la parole.
+narrateur|Nino caresse encore le chat dessiné.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6918,7 +7339,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>Trois goûters attendent, tout proches. Une pomme, un yaourt, ou un morceau de pain ? On tend. On attend.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7082,7 +7503,9 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|Trois goûters attendent, tout proches.
+maman|Une pomme, un yaourt, ou un morceau de pain ?
+papa|On tend. On attend.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7110,7 +7533,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Jules montre le livre, puis la pomme. Le camarade pointe. Jules attend. Il tend un jouet. Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Papa coupe une pomme jaune. La peau est lisse, un peu froide. Une goutte de jus brille sur la table. Tu veux un quartier, Nino ? Nino regarde la pomme. Il ne dit rien. Raphaël attend. Je lui tends le quartier. Nino prend la pomme. Il croque, tout petit. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. Une goutte de jus reste au bord de la page. On a encore le livre, sur la table. On peut attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7250,8 +7673,26 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Jules montre le livre, puis la pomme. Le camarade pointe. Jules attend. Il tend un jouet.
-papa|Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>narrateur|Papa coupe une pomme jaune.
+narrateur|La peau est lisse, un peu froide.
+narrateur|Une goutte de jus brille sur la table.
+papa|Tu veux un quartier, Nino ?
+narrateur|Nino regarde la pomme.
+narrateur|Il ne dit rien.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le quartier.
+narrateur|Nino prend la pomme.
+narrateur|Il croque, tout petit.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+papa|On peut jouer ensemble.
+maman|Bravo, Raphaël.
+maman|Tu as tendu, sans presser.
+narrateur|Une goutte de jus reste au bord de la page.
+narrateur|On a encore le livre, sur la table.
+maman|On peut attendre.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7279,7 +7720,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Un animal de la maison attend, tout près. Le chat, le chien, ou la poule ? On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7443,7 +7884,9 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Un animal de la maison attend, tout près.
+papa|Le chat, le chien, ou la poule ?
+maman|On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -7475,7 +7918,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le livre. Puis une pomme. Puis le chat. Un galet est encore chaud. Maman n'est pas loin. Jules les rejoint. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chat de la maison s'étire sur la chaise. Son dos est chaud, tout soyeux. Il fait un petit ronron. Le chat aime le calme, lui aussi. Nino tend un doigt, tout lentement. Raphaël attend. Je lui tends le jouet souris. Nino pose le jouet près du chat. On peut attendre. On peut tendre un jouet. On ne force pas la parole. Bravo, Raphaël. Tu as su attendre. Le chat vrai ressemble au chat du livre. Raphaël a encore le livre. Il reste un quartier de pomme. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7615,7 +8058,27 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le livre. Puis une pomme. Puis le chat. Un galet est encore chaud. Maman n'est pas loin. Jules les rejoint. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat de la maison s'étire sur la chaise.
+narrateur|Son dos est chaud, tout soyeux.
+narrateur|Il fait un petit ronron.
+maman|Le chat aime le calme, lui aussi.
+narrateur|Nino tend un doigt, tout lentement.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le jouet souris.
+narrateur|Nino pose le jouet près du chat.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+papa|Bravo, Raphaël.
+papa|Tu as su attendre.
+narrateur|Le chat vrai ressemble au chat du livre.
+narrateur|Raphaël a encore le livre.
+narrateur|Il reste un quartier de pomme.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7643,7 +8106,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec le livre. Nino a pris la pomme, sans parler. Ils ont vu le chat, tout ensemble. Le chat se rendort, tout rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7783,7 +8246,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec le livre.
+narrateur|Nino a pris la pomme, sans parler.
+narrateur|Ils ont vu le chat, tout ensemble.
+narrateur|Le chat se rendort, tout rond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7811,7 +8283,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Jules s'arrête près de le chien. une pomme est rangé. Il y a des miettes sur la table. Jules range le livre dans sa tête, comme un souvenir. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chien gratte doucement la porte. Ses poils sentent l'herbe mouillée. Il fait un wouaf, tout amical. Le chien est content, tout simplement. Nino recule un peu, puis avance. Raphaël attend, tout près. Je lui tends la balle molle. Nino pose la balle au sol. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. C'est du bon travail. Une page claque, tout petit, près du chien. Raphaël a encore le livre. Il reste un quartier de pomme. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7951,7 +8423,28 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Jules s'arrête près de le chien. une pomme est rangé. Il y a des miettes sur la table. Jules range le livre dans sa tête, comme un souvenir. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien gratte doucement la porte.
+narrateur|Ses poils sentent l'herbe mouillée.
+narrateur|Il fait un wouaf, tout amical.
+papa|Le chien est content, tout simplement.
+narrateur|Nino recule un peu, puis avance.
+narrateur|Raphaël attend, tout près.
+enfant-m|Je lui tends la balle molle.
+narrateur|Nino pose la balle au sol.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Une page claque, tout petit, près du chien.
+narrateur|Raphaël a encore le livre.
+narrateur|Il reste un quartier de pomme.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -7983,7 +8476,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec le livre. Nino a pris la pomme, sans parler. Ils ont vu le chien, tout ensemble. Le chien pose la tête, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8123,7 +8616,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec le livre.
+narrateur|Nino a pris la pomme, sans parler.
+narrateur|Ils ont vu le chien, tout ensemble.
+narrateur|Le chien pose la tête, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8151,7 +8653,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Jules se souvient de le livre. Et de une pomme. Et de la poule. Les chaussures font toc toc. Jules caresse le doudou. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule picore près du bac, dehors. Ses plumes sont rousses, un peu mouillées. Elle fait cot cot, tout bas. On la regarde, tout doux. Nino s'accroupit, sans un mot. Raphaël attend à côté. Je lui tends le seau de grains. Nino pose le seau, tout lentement. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. La poule du livre a un bec trop rond. Raphaël a encore le livre. Il reste un quartier de pomme. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8291,7 +8793,28 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Jules se souvient de le livre. Et de une pomme. Et de la poule. Les chaussures font toc toc. Jules caresse le doudou. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près du bac, dehors.
+narrateur|Ses plumes sont rousses, un peu mouillées.
+narrateur|Elle fait cot cot, tout bas.
+maman|On la regarde, tout doux.
+narrateur|Nino s'accroupit, sans un mot.
+narrateur|Raphaël attend à côté.
+enfant-m|Je lui tends le seau de grains.
+narrateur|Nino pose le seau, tout lentement.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo, Raphaël.
+papa|Tu as tendu, sans presser.
+narrateur|La poule du livre a un bec trop rond.
+narrateur|Raphaël a encore le livre.
+narrateur|Il reste un quartier de pomme.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8319,7 +8842,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec le livre. Nino a pris la pomme, sans parler. Ils ont vu la poule, tout ensemble. La poule rentre sous l'auvent, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8459,7 +8982,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec le livre.
+narrateur|Nino a pris la pomme, sans parler.
+narrateur|Ils ont vu la poule, tout ensemble.
+narrateur|La poule rentre sous l'auvent, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8487,7 +9019,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Jules montre le livre, puis le yaourt. Le camarade reste silencieux. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Maman sort un yaourt du saladier froid. Le pot est lisse, un peu mouillé. Une cuillère tape le bord. Le yaourt est là, Nino. Nino tapote le pot. Raphaël attend, les mains sages. Je lui tends la cuillère. Nino prend la cuillère. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. Tu as su attendre. Une goutte blanche reste sur la nappe. Le livre est un peu loin du pot froid. On a encore le livre, sur la table. On peut attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8627,7 +9159,25 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Jules montre le livre, puis le yaourt. Le camarade reste silencieux. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>narrateur|Maman sort un yaourt du saladier froid.
+narrateur|Le pot est lisse, un peu mouillé.
+narrateur|Une cuillère tape le bord.
+maman|Le yaourt est là, Nino.
+narrateur|Nino tapote le pot.
+narrateur|Raphaël attend, les mains sages.
+enfant-m|Je lui tends la cuillère.
+narrateur|Nino prend la cuillère.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Tu as su attendre.
+narrateur|Une goutte blanche reste sur la nappe.
+narrateur|Le livre est un peu loin du pot froid.
+narrateur|On a encore le livre, sur la table.
+maman|On peut attendre.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8655,7 +9205,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Un animal de la maison attend, tout près. Le chat, le chien, ou la poule ? On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8819,7 +9369,9 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Un animal de la maison attend, tout près.
+papa|Le chat, le chien, ou la poule ?
+maman|On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -8851,7 +9403,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec le chat. Après un yaourt. Près de le livre. Jules s'arrête. On rit un peu. Jules boit une gorgée d'eau. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chat de la maison s'étire sur la chaise. Son dos est chaud, tout soyeux. Il fait un petit ronron. Le chat aime le calme, lui aussi. Nino tend un doigt, tout lentement. Raphaël attend. Je lui tends le jouet souris. Nino pose le jouet près du chat. On peut attendre. On peut tendre un jouet. On ne force pas la parole. Bravo, Raphaël. Tu as su attendre. Le livre reste ouvert sur les genoux calmes. Raphaël a encore le livre. Il reste un peu de yaourt. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8991,7 +9543,27 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec le chat. Après un yaourt. Près de le livre. Jules s'arrête. On rit un peu. Jules boit une gorgée d'eau. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat de la maison s'étire sur la chaise.
+narrateur|Son dos est chaud, tout soyeux.
+narrateur|Il fait un petit ronron.
+maman|Le chat aime le calme, lui aussi.
+narrateur|Nino tend un doigt, tout lentement.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le jouet souris.
+narrateur|Nino pose le jouet près du chat.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+papa|Bravo, Raphaël.
+papa|Tu as su attendre.
+narrateur|Le livre reste ouvert sur les genoux calmes.
+narrateur|Raphaël a encore le livre.
+narrateur|Il reste un peu de yaourt.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9019,7 +9591,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec le livre. Nino a pris le yaourt, sans parler. Ils ont vu le chat, tout ensemble. Le chat se rendort, tout rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9159,7 +9731,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec le livre.
+narrateur|Nino a pris le yaourt, sans parler.
+narrateur|Ils ont vu le chat, tout ensemble.
+narrateur|Le chat se rendort, tout rond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9187,7 +9768,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Jules range un yaourt. le chien reste près de le livre. Une chaussette est encore sablée. Jules prend la main de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chien gratte doucement la porte. Ses poils sentent l'herbe mouillée. Il fait un wouaf, tout amical. Le chien est content, tout simplement. Nino recule un peu, puis avance. Raphaël attend, tout près. Je lui tends la balle molle. Nino pose la balle au sol. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. C'est du bon travail. Le chien attend, comme Nino, tout sage. Raphaël a encore le livre. Il reste un peu de yaourt. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9327,7 +9908,28 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Jules range un yaourt. le chien reste près de le livre. Une chaussette est encore sablée. Jules prend la main de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien gratte doucement la porte.
+narrateur|Ses poils sentent l'herbe mouillée.
+narrateur|Il fait un wouaf, tout amical.
+papa|Le chien est content, tout simplement.
+narrateur|Nino recule un peu, puis avance.
+narrateur|Raphaël attend, tout près.
+enfant-m|Je lui tends la balle molle.
+narrateur|Nino pose la balle au sol.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le chien attend, comme Nino, tout sage.
+narrateur|Raphaël a encore le livre.
+narrateur|Il reste un peu de yaourt.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -9359,7 +9961,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec le livre. Nino a pris le yaourt, sans parler. Ils ont vu le chien, tout ensemble. Le chien pose la tête, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9499,7 +10101,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec le livre.
+narrateur|Nino a pris le yaourt, sans parler.
+narrateur|Ils ont vu le chien, tout ensemble.
+narrateur|Le chien pose la tête, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9527,7 +10138,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>La poule est là. un yaourt aussi. le livre reste dans le souvenir. La couverture est douce. Jules chuchote : c'est fini. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule picore près du bac, dehors. Ses plumes sont rousses, un peu mouillées. Elle fait cot cot, tout bas. On la regarde, tout doux. Nino s'accroupit, sans un mot. Raphaël attend à côté. Je lui tends le seau de grains. Nino pose le seau, tout lentement. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. Une image de poule brille, un peu tachée. Raphaël a encore le livre. Il reste un peu de yaourt. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9667,7 +10278,28 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|La poule est là. un yaourt aussi. le livre reste dans le souvenir. La couverture est douce. Jules chuchote : c'est fini. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près du bac, dehors.
+narrateur|Ses plumes sont rousses, un peu mouillées.
+narrateur|Elle fait cot cot, tout bas.
+maman|On la regarde, tout doux.
+narrateur|Nino s'accroupit, sans un mot.
+narrateur|Raphaël attend à côté.
+enfant-m|Je lui tends le seau de grains.
+narrateur|Nino pose le seau, tout lentement.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo, Raphaël.
+papa|Tu as tendu, sans presser.
+narrateur|Une image de poule brille, un peu tachée.
+narrateur|Raphaël a encore le livre.
+narrateur|Il reste un peu de yaourt.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9695,7 +10327,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec le livre. Nino a pris le yaourt, sans parler. Ils ont vu la poule, tout ensemble. La poule rentre sous l'auvent, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9835,7 +10467,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec le livre.
+narrateur|Nino a pris le yaourt, sans parler.
+narrateur|Ils ont vu la poule, tout ensemble.
+narrateur|La poule rentre sous l'auvent, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9863,7 +10504,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Jules montre le livre, puis le pain. Le camarade sourit. Jules attend. Il tend un jouet. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Papa tend un morceau de pain. La croûte est encore tiède. Ça sent le four, tout doux. Tu le sens, Nino ? Nino approche le pain. Il ne parle pas. Raphaël attend la fin du silence. Je lui tends le pain. Nino prend le morceau. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Une miette reste près du cube. Une miette marque la page, tout doux. On a encore le livre, sur la table. On peut attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -10003,7 +10644,25 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Jules montre le livre, puis le pain. Le camarade sourit. Jules attend. Il tend un jouet. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>narrateur|Papa tend un morceau de pain.
+narrateur|La croûte est encore tiède.
+narrateur|Ça sent le four, tout doux.
+papa|Tu le sens, Nino ?
+narrateur|Nino approche le pain.
+narrateur|Il ne parle pas.
+narrateur|Raphaël attend la fin du silence.
+enfant-m|Je lui tends le pain.
+narrateur|Nino prend le morceau.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+papa|On peut jouer ensemble.
+maman|Bravo, Raphaël.
+narrateur|Une miette reste près du cube.
+narrateur|Une miette marque la page, tout doux.
+narrateur|On a encore le livre, sur la table.
+maman|On peut attendre.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10031,7 +10690,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Un animal de la maison attend, tout près. Le chat, le chien, ou la poule ? On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10195,7 +10854,9 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Un animal de la maison attend, tout près.
+papa|Le chat, le chien, ou la poule ?
+maman|On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -10227,7 +10888,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le chat. un morceau de pain est rangé. le livre est fini. Un panier est posé sur le banc. Jules dit merci à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chat de la maison s'étire sur la chaise. Son dos est chaud, tout soyeux. Il fait un petit ronron. Le chat aime le calme, lui aussi. Nino tend un doigt, tout lentement. Raphaël attend. Je lui tends le jouet souris. Nino pose le jouet près du chat. On peut attendre. On peut tendre un jouet. On ne force pas la parole. Bravo, Raphaël. Tu as su attendre. Une miette sèche au bord de la page. Raphaël a encore le livre. Il reste une croûte de pain. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10367,7 +11028,27 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le chat. un morceau de pain est rangé. le livre est fini. Un panier est posé sur le banc. Jules dit merci à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat de la maison s'étire sur la chaise.
+narrateur|Son dos est chaud, tout soyeux.
+narrateur|Il fait un petit ronron.
+maman|Le chat aime le calme, lui aussi.
+narrateur|Nino tend un doigt, tout lentement.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le jouet souris.
+narrateur|Nino pose le jouet près du chat.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+papa|Bravo, Raphaël.
+papa|Tu as su attendre.
+narrateur|Une miette sèche au bord de la page.
+narrateur|Raphaël a encore le livre.
+narrateur|Il reste une croûte de pain.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10395,7 +11076,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec le livre. Nino a pris le pain, sans parler. Ils ont vu le chat, tout ensemble. Le chat se rendort, tout rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10535,7 +11216,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec le livre.
+narrateur|Nino a pris le pain, sans parler.
+narrateur|Ils ont vu le chat, tout ensemble.
+narrateur|Le chat se rendort, tout rond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10563,7 +11253,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de le chien. Jules pose un morceau de pain. le livre est derrière. L'eau coule, tout petit bruit. Jules souffle, puis sourit à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chien gratte doucement la porte. Ses poils sentent l'herbe mouillée. Il fait un wouaf, tout amical. Le chien est content, tout simplement. Nino recule un peu, puis avance. Raphaël attend, tout près. Je lui tends la balle molle. Nino pose la balle au sol. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. C'est du bon travail. Le chien écoute le papier, tout curieux. Raphaël a encore le livre. Il reste une croûte de pain. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10703,7 +11393,28 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de le chien. Jules pose un morceau de pain. le livre est derrière. L'eau coule, tout petit bruit. Jules souffle, puis sourit à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien gratte doucement la porte.
+narrateur|Ses poils sentent l'herbe mouillée.
+narrateur|Il fait un wouaf, tout amical.
+papa|Le chien est content, tout simplement.
+narrateur|Nino recule un peu, puis avance.
+narrateur|Raphaël attend, tout près.
+enfant-m|Je lui tends la balle molle.
+narrateur|Nino pose la balle au sol.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le chien écoute le papier, tout curieux.
+narrateur|Raphaël a encore le livre.
+narrateur|Il reste une croûte de pain.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -10735,7 +11446,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec le livre. Nino a pris le pain, sans parler. Ils ont vu le chien, tout ensemble. Le chien pose la tête, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10875,7 +11586,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec le livre.
+narrateur|Nino a pris le pain, sans parler.
+narrateur|Ils ont vu le chien, tout ensemble.
+narrateur|Le chien pose la tête, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10903,7 +11623,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Jules montre la poule. Papa a vu le livre. Et un morceau de pain. Un crochet tient bien le manteau. Jules range la tasse. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule picore près du bac, dehors. Ses plumes sont rousses, un peu mouillées. Elle fait cot cot, tout bas. On la regarde, tout doux. Nino s'accroupit, sans un mot. Raphaël attend à côté. Je lui tends le seau de grains. Nino pose le seau, tout lentement. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. La poule s'éloigne. Le livre reste ouvert. Raphaël a encore le livre. Il reste une croûte de pain. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11043,7 +11763,29 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Jules montre la poule. Papa a vu le livre. Et un morceau de pain. Un crochet tient bien le manteau. Jules range la tasse. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près du bac, dehors.
+narrateur|Ses plumes sont rousses, un peu mouillées.
+narrateur|Elle fait cot cot, tout bas.
+maman|On la regarde, tout doux.
+narrateur|Nino s'accroupit, sans un mot.
+narrateur|Raphaël attend à côté.
+enfant-m|Je lui tends le seau de grains.
+narrateur|Nino pose le seau, tout lentement.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo, Raphaël.
+papa|Tu as tendu, sans presser.
+narrateur|La poule s'éloigne.
+narrateur|Le livre reste ouvert.
+narrateur|Raphaël a encore le livre.
+narrateur|Il reste une croûte de pain.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11071,7 +11813,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec le livre. Nino a pris le pain, sans parler. Ils ont vu la poule, tout ensemble. La poule rentre sous l'auvent, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11211,7 +11953,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec le livre.
+narrateur|Nino a pris le pain, sans parler.
+narrateur|Ils ont vu la poule, tout ensemble.
+narrateur|La poule rentre sous l'auvent, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11239,7 +11990,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules sort la dînette. Le camarade qui parle peu s'assoit. Jules attend. Il tend une tasse. Pas forcer la parole. Une tasse cliquette. Maman reste près d'eux. On peut jouer ensemble.</t>
+          <t>Raphaël sort la dînette. Une tasse cliquette, tout creux. Une cuillère miniature est encore tiède. Nino s'assoit près de la nappe. Il regarde la petite casserole. Raphaël attend un petit moment. Je lui tends la tasse. Nino prend la tasse. Il la pose devant lui. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On n'imite pas. On peut jouer ensemble. Raphaël verse de l'air, tout sérieux. Bravo, Raphaël. Tu as tendu un jouet. La tasse reste entre les deux.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11379,7 +12130,24 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Jules sort la dînette. Le camarade qui parle peu s'assoit. Jules attend. Il tend une tasse. Pas forcer la parole. Une tasse cliquette. Maman reste près d'eux. On peut jouer ensemble.</t>
+          <t>narrateur|Raphaël sort la dînette.
+narrateur|Une tasse cliquette, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+narrateur|Nino s'assoit près de la nappe.
+narrateur|Il regarde la petite casserole.
+narrateur|Raphaël attend un petit moment.
+enfant-m|Je lui tends la tasse.
+narrateur|Nino prend la tasse.
+narrateur|Il la pose devant lui.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+papa|On n'imite pas.
+maman|On peut jouer ensemble.
+narrateur|Raphaël verse de l'air, tout sérieux.
+papa|Bravo, Raphaël.
+papa|Tu as tendu un jouet.
+narrateur|La tasse reste entre les deux.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11407,7 +12175,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On force la parole ?</t>
+          <t>Nino tient la tasse. On attend sa parole ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11563,7 +12331,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On force la parole ?</t>
+          <t>narrateur|Nino tient la tasse.
+maman|On attend sa parole ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11591,7 +12360,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On attend. On tend un jouet. Jules hoche la tête. On continue, avec papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Oui. On attend. On tend un jouet. La petite tasse cliquette encore. J'attends. Bravo. On ne force pas la parole. On peut jouer ensemble. Nino tient la cuillère, tout silencieux.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11735,7 +12504,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On attend. On tend un jouet. Jules hoche la tête. On continue, avec papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On attend.
+papa|On tend un jouet.
+narrateur|La petite tasse cliquette encore.
+enfant-m|J'attends.
+maman|Bravo.
+maman|On ne force pas la parole.
+papa|On peut jouer ensemble.
+narrateur|Nino tient la cuillère, tout silencieux.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11763,7 +12540,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>Trois goûters attendent, tout proches. Une pomme, un yaourt, ou un morceau de pain ? On tend. On attend.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11927,7 +12704,9 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|Trois goûters attendent, tout proches.
+maman|Une pomme, un yaourt, ou un morceau de pain ?
+papa|On tend. On attend.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11955,7 +12734,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Jules tend une tasse, puis une pomme. Le camarade prend la tasse. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Papa coupe une pomme jaune. La peau est lisse, un peu froide. Une goutte de jus brille sur la table. Tu veux un quartier, Nino ? Nino regarde la pomme. Il ne dit rien. Raphaël attend. Je lui tends le quartier. Nino prend la pomme. Il croque, tout petit. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. La petite assiette est près du quartier. On a encore la dînette, sur la table. On peut attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12095,7 +12874,26 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Jules tend une tasse, puis une pomme. Le camarade prend la tasse. Jules attend. Pas forcer la parole. Papa reste tout près. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>narrateur|Papa coupe une pomme jaune.
+narrateur|La peau est lisse, un peu froide.
+narrateur|Une goutte de jus brille sur la table.
+papa|Tu veux un quartier, Nino ?
+narrateur|Nino regarde la pomme.
+narrateur|Il ne dit rien.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le quartier.
+narrateur|Nino prend la pomme.
+narrateur|Il croque, tout petit.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+papa|On peut jouer ensemble.
+maman|Bravo, Raphaël.
+maman|Tu as tendu, sans presser.
+narrateur|La petite assiette est près du quartier.
+narrateur|On a encore la dînette, sur la table.
+maman|On peut attendre.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12123,7 +12921,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Un animal de la maison attend, tout près. Le chat, le chien, ou la poule ? On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12287,7 +13085,9 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Un animal de la maison attend, tout près.
+papa|Le chat, le chien, ou la poule ?
+maman|On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -12319,7 +13119,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi la dînette. Puis une pomme. Puis le chat. Le vent est doux. Jules plie un pull. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chat de la maison s'étire sur la chaise. Son dos est chaud, tout soyeux. Il fait un petit ronron. Le chat aime le calme, lui aussi. Nino tend un doigt, tout lentement. Raphaël attend. Je lui tends le jouet souris. Nino pose le jouet près du chat. On peut attendre. On peut tendre un jouet. On ne force pas la parole. Bravo, Raphaël. Tu as su attendre. La petite tasse est près de la gamelle. Raphaël a encore la dînette. Il reste un quartier de pomme. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12459,7 +13259,27 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi la dînette. Puis une pomme. Puis le chat. Le vent est doux. Jules plie un pull. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat de la maison s'étire sur la chaise.
+narrateur|Son dos est chaud, tout soyeux.
+narrateur|Il fait un petit ronron.
+maman|Le chat aime le calme, lui aussi.
+narrateur|Nino tend un doigt, tout lentement.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le jouet souris.
+narrateur|Nino pose le jouet près du chat.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+papa|Bravo, Raphaël.
+papa|Tu as su attendre.
+narrateur|La petite tasse est près de la gamelle.
+narrateur|Raphaël a encore la dînette.
+narrateur|Il reste un quartier de pomme.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12487,7 +13307,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec la dînette. Nino a pris la pomme, sans parler. Ils ont vu le chat, tout ensemble. Le chat se rendort, tout rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12627,7 +13447,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec la dînette.
+narrateur|Nino a pris la pomme, sans parler.
+narrateur|Ils ont vu le chat, tout ensemble.
+narrateur|Le chat se rendort, tout rond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12655,7 +13484,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Jules s'arrête près de le chien. une pomme est rangé. On écoute jusqu'au bout. Jules sourit. Papa sourit aussi. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chien gratte doucement la porte. Ses poils sentent l'herbe mouillée. Il fait un wouaf, tout amical. Le chien est content, tout simplement. Nino recule un peu, puis avance. Raphaël attend, tout près. Je lui tends la balle molle. Nino pose la balle au sol. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. C'est du bon travail. La casserole miniature sonne près du collier. Raphaël a encore la dînette. Il reste un quartier de pomme. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12795,7 +13624,28 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Jules s'arrête près de le chien. une pomme est rangé. On écoute jusqu'au bout. Jules sourit. Papa sourit aussi. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien gratte doucement la porte.
+narrateur|Ses poils sentent l'herbe mouillée.
+narrateur|Il fait un wouaf, tout amical.
+papa|Le chien est content, tout simplement.
+narrateur|Nino recule un peu, puis avance.
+narrateur|Raphaël attend, tout près.
+enfant-m|Je lui tends la balle molle.
+narrateur|Nino pose la balle au sol.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|La casserole miniature sonne près du collier.
+narrateur|Raphaël a encore la dînette.
+narrateur|Il reste un quartier de pomme.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -12827,7 +13677,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec la dînette. Nino a pris la pomme, sans parler. Ils ont vu le chien, tout ensemble. Le chien pose la tête, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12967,7 +13817,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec la dînette.
+narrateur|Nino a pris la pomme, sans parler.
+narrateur|Ils ont vu le chien, tout ensemble.
+narrateur|Le chien pose la tête, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12995,7 +13854,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Jules se souvient de la dînette. Et de une pomme. Et de la poule. Un linge sèche à l'air. Jules enfile ses chaussons. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule picore près du bac, dehors. Ses plumes sont rousses, un peu mouillées. Elle fait cot cot, tout bas. On la regarde, tout doux. Nino s'accroupit, sans un mot. Raphaël attend à côté. Je lui tends le seau de grains. Nino pose le seau, tout lentement. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. Une petite assiette a une plume collée. Raphaël a encore la dînette. Il reste un quartier de pomme. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13135,7 +13994,28 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Jules se souvient de la dînette. Et de une pomme. Et de la poule. Un linge sèche à l'air. Jules enfile ses chaussons. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près du bac, dehors.
+narrateur|Ses plumes sont rousses, un peu mouillées.
+narrateur|Elle fait cot cot, tout bas.
+maman|On la regarde, tout doux.
+narrateur|Nino s'accroupit, sans un mot.
+narrateur|Raphaël attend à côté.
+enfant-m|Je lui tends le seau de grains.
+narrateur|Nino pose le seau, tout lentement.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo, Raphaël.
+papa|Tu as tendu, sans presser.
+narrateur|Une petite assiette a une plume collée.
+narrateur|Raphaël a encore la dînette.
+narrateur|Il reste un quartier de pomme.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13163,7 +14043,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec la dînette. Nino a pris la pomme, sans parler. Ils ont vu la poule, tout ensemble. La poule rentre sous l'auvent, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13303,7 +14183,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec la dînette.
+narrateur|Nino a pris la pomme, sans parler.
+narrateur|Ils ont vu la poule, tout ensemble.
+narrateur|La poule rentre sous l'auvent, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13331,7 +14220,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Jules tend une tasse, puis un yaourt. Le camarade tapote. Jules attend. Il tend un jouet. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Maman sort un yaourt du saladier froid. Le pot est lisse, un peu mouillé. Une cuillère tape le bord. Le yaourt est là, Nino. Nino tapote le pot. Raphaël attend, les mains sages. Je lui tends la cuillère. Nino prend la cuillère. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. Tu as su attendre. Une goutte blanche reste sur la nappe. La petite cuillère tremble près du pot. On a encore la dînette, sur la table. On peut attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13471,7 +14360,25 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Jules tend une tasse, puis un yaourt. Le camarade tapote. Jules attend. Il tend un jouet. Papa montre le geste, lentement. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>narrateur|Maman sort un yaourt du saladier froid.
+narrateur|Le pot est lisse, un peu mouillé.
+narrateur|Une cuillère tape le bord.
+maman|Le yaourt est là, Nino.
+narrateur|Nino tapote le pot.
+narrateur|Raphaël attend, les mains sages.
+enfant-m|Je lui tends la cuillère.
+narrateur|Nino prend la cuillère.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Tu as su attendre.
+narrateur|Une goutte blanche reste sur la nappe.
+narrateur|La petite cuillère tremble près du pot.
+narrateur|On a encore la dînette, sur la table.
+maman|On peut attendre.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13499,7 +14406,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Un animal de la maison attend, tout près. Le chat, le chien, ou la poule ? On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13663,7 +14570,9 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Un animal de la maison attend, tout près.
+papa|Le chat, le chien, ou la poule ?
+maman|On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -13695,7 +14604,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec le chat. Après un yaourt. Près de la dînette. Jules s'arrête. On se tient la main. Jules montre le chat à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chat de la maison s'étire sur la chaise. Son dos est chaud, tout soyeux. Il fait un petit ronron. Le chat aime le calme, lui aussi. Nino tend un doigt, tout lentement. Raphaël attend. Je lui tends le jouet souris. Nino pose le jouet près du chat. On peut attendre. On peut tendre un jouet. On ne force pas la parole. Bravo, Raphaël. Tu as su attendre. Le chat tape la tasse, tout léger. Raphaël a encore la dînette. Il reste un peu de yaourt. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13835,7 +14744,27 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec le chat. Après un yaourt. Près de la dînette. Jules s'arrête. On se tient la main. Jules montre le chat à papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat de la maison s'étire sur la chaise.
+narrateur|Son dos est chaud, tout soyeux.
+narrateur|Il fait un petit ronron.
+maman|Le chat aime le calme, lui aussi.
+narrateur|Nino tend un doigt, tout lentement.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le jouet souris.
+narrateur|Nino pose le jouet près du chat.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+papa|Bravo, Raphaël.
+papa|Tu as su attendre.
+narrateur|Le chat tape la tasse, tout léger.
+narrateur|Raphaël a encore la dînette.
+narrateur|Il reste un peu de yaourt.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13863,7 +14792,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec la dînette. Nino a pris le yaourt, sans parler. Ils ont vu le chat, tout ensemble. Le chat se rendort, tout rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14003,7 +14932,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec la dînette.
+narrateur|Nino a pris le yaourt, sans parler.
+narrateur|Ils ont vu le chat, tout ensemble.
+narrateur|Le chat se rendort, tout rond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14031,7 +14969,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Jules range un yaourt. le chien reste près de la dînette. On entend un oiseau. Jules pose un yaourt à sa place. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chien gratte doucement la porte. Ses poils sentent l'herbe mouillée. Il fait un wouaf, tout amical. Le chien est content, tout simplement. Nino recule un peu, puis avance. Raphaël attend, tout près. Je lui tends la balle molle. Nino pose la balle au sol. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. C'est du bon travail. Le chien laisse la dînette tranquille. Raphaël a encore la dînette. Il reste un peu de yaourt. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14171,7 +15109,28 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Jules range un yaourt. le chien reste près de la dînette. On entend un oiseau. Jules pose un yaourt à sa place. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien gratte doucement la porte.
+narrateur|Ses poils sentent l'herbe mouillée.
+narrateur|Il fait un wouaf, tout amical.
+papa|Le chien est content, tout simplement.
+narrateur|Nino recule un peu, puis avance.
+narrateur|Raphaël attend, tout près.
+enfant-m|Je lui tends la balle molle.
+narrateur|Nino pose la balle au sol.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le chien laisse la dînette tranquille.
+narrateur|Raphaël a encore la dînette.
+narrateur|Il reste un peu de yaourt.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -14203,7 +15162,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec la dînette. Nino a pris le yaourt, sans parler. Ils ont vu le chien, tout ensemble. Le chien pose la tête, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14343,7 +15302,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec la dînette.
+narrateur|Nino a pris le yaourt, sans parler.
+narrateur|Ils ont vu le chien, tout ensemble.
+narrateur|Le chien pose la tête, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14371,7 +15339,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>La poule est là. un yaourt aussi. la dînette reste dans le souvenir. La lumière est claire. Jules serre la main de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule picore près du bac, dehors. Ses plumes sont rousses, un peu mouillées. Elle fait cot cot, tout bas. On la regarde, tout doux. Nino s'accroupit, sans un mot. Raphaël attend à côté. Je lui tends le seau de grains. Nino pose le seau, tout lentement. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. La poule picore. La tasse cliquette encore. Raphaël a encore la dînette. Il reste un peu de yaourt. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14511,7 +15479,29 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|La poule est là. un yaourt aussi. la dînette reste dans le souvenir. La lumière est claire. Jules serre la main de papa. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près du bac, dehors.
+narrateur|Ses plumes sont rousses, un peu mouillées.
+narrateur|Elle fait cot cot, tout bas.
+maman|On la regarde, tout doux.
+narrateur|Nino s'accroupit, sans un mot.
+narrateur|Raphaël attend à côté.
+enfant-m|Je lui tends le seau de grains.
+narrateur|Nino pose le seau, tout lentement.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo, Raphaël.
+papa|Tu as tendu, sans presser.
+narrateur|La poule picore.
+narrateur|La tasse cliquette encore.
+narrateur|Raphaël a encore la dînette.
+narrateur|Il reste un peu de yaourt.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14539,7 +15529,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec la dînette. Nino a pris le yaourt, sans parler. Ils ont vu la poule, tout ensemble. La poule rentre sous l'auvent, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14679,7 +15669,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec la dînette.
+narrateur|Nino a pris le yaourt, sans parler.
+narrateur|Ils ont vu la poule, tout ensemble.
+narrateur|La poule rentre sous l'auvent, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14707,7 +15706,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Jules tend une tasse, puis le pain. Le camarade s'assoit. Jules attend. Pas forcer la parole. Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>Papa tend un morceau de pain. La croûte est encore tiède. Ça sent le four, tout doux. Tu le sens, Nino ? Nino approche le pain. Il ne parle pas. Raphaël attend la fin du silence. Je lui tends le pain. Nino prend le morceau. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Une miette reste près du cube. La dînette sent encore le pain chaud. On a encore la dînette, sur la table. On peut attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14847,8 +15846,25 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Jules tend une tasse, puis le pain. Le camarade s'assoit. Jules attend. Pas forcer la parole.
-papa|Je suis là. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut jouer ensemble.</t>
+          <t>narrateur|Papa tend un morceau de pain.
+narrateur|La croûte est encore tiède.
+narrateur|Ça sent le four, tout doux.
+papa|Tu le sens, Nino ?
+narrateur|Nino approche le pain.
+narrateur|Il ne parle pas.
+narrateur|Raphaël attend la fin du silence.
+enfant-m|Je lui tends le pain.
+narrateur|Nino prend le morceau.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+papa|On peut jouer ensemble.
+maman|Bravo, Raphaël.
+narrateur|Une miette reste près du cube.
+narrateur|La dînette sent encore le pain chaud.
+narrateur|On a encore la dînette, sur la table.
+maman|On peut attendre.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14876,7 +15892,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Un animal de la maison attend, tout près. Le chat, le chien, ou la poule ? On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15040,7 +16056,9 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Un animal de la maison attend, tout près.
+papa|Le chat, le chien, ou la poule ?
+maman|On tend un jouet. On attend.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
@@ -15072,7 +16090,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le chat. un morceau de pain est rangé. la dînette est fini. Une tasse cliquette. Jules écoute papa encore une fois. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chat de la maison s'étire sur la chaise. Son dos est chaud, tout soyeux. Il fait un petit ronron. Le chat aime le calme, lui aussi. Nino tend un doigt, tout lentement. Raphaël attend. Je lui tends le jouet souris. Nino pose le jouet près du chat. On peut attendre. On peut tendre un jouet. On ne force pas la parole. Bravo, Raphaël. Tu as su attendre. Le chat se recroqueville près de la nappe. Raphaël a encore la dînette. Il reste une croûte de pain. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15212,7 +16230,27 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le chat. un morceau de pain est rangé. la dînette est fini. Une tasse cliquette. Jules écoute papa encore une fois. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat de la maison s'étire sur la chaise.
+narrateur|Son dos est chaud, tout soyeux.
+narrateur|Il fait un petit ronron.
+maman|Le chat aime le calme, lui aussi.
+narrateur|Nino tend un doigt, tout lentement.
+narrateur|Raphaël attend.
+enfant-m|Je lui tends le jouet souris.
+narrateur|Nino pose le jouet près du chat.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+papa|Bravo, Raphaël.
+papa|Tu as su attendre.
+narrateur|Le chat se recroqueville près de la nappe.
+narrateur|Raphaël a encore la dînette.
+narrateur|Il reste une croûte de pain.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15240,7 +16278,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec la dînette. Nino a pris le pain, sans parler. Ils ont vu le chat, tout ensemble. Le chat se rendort, tout rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15380,7 +16418,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec la dînette.
+narrateur|Nino a pris le pain, sans parler.
+narrateur|Ils ont vu le chat, tout ensemble.
+narrateur|Le chat se rendort, tout rond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15408,7 +16455,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de le chien. Jules pose un morceau de pain. la dînette est derrière. Un chat miaule une fois. Jules tend le chien à maman. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>Le chien gratte doucement la porte. Ses poils sentent l'herbe mouillée. Il fait un wouaf, tout amical. Le chien est content, tout simplement. Nino recule un peu, puis avance. Raphaël attend, tout près. Je lui tends la balle molle. Nino pose la balle au sol. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo. C'est du bon travail. Le chien s'allonge. La dînette se range. Raphaël a encore la dînette. Il reste une croûte de pain. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15548,7 +16595,29 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de le chien. Jules pose un morceau de pain. la dînette est derrière. Un chat miaule une fois. Jules tend le chien à maman. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien gratte doucement la porte.
+narrateur|Ses poils sentent l'herbe mouillée.
+narrateur|Il fait un wouaf, tout amical.
+papa|Le chien est content, tout simplement.
+narrateur|Nino recule un peu, puis avance.
+narrateur|Raphaël attend, tout près.
+enfant-m|Je lui tends la balle molle.
+narrateur|Nino pose la balle au sol.
+maman|On peut attendre.
+maman|On peut tendre un jouet.
+papa|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le chien s'allonge.
+narrateur|La dînette se range.
+narrateur|Raphaël a encore la dînette.
+narrateur|Il reste une croûte de pain.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -15580,7 +16649,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec la dînette. Nino a pris le pain, sans parler. Ils ont vu le chien, tout ensemble. Le chien pose la tête, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15720,7 +16789,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec la dînette.
+narrateur|Nino a pris le pain, sans parler.
+narrateur|Ils ont vu le chien, tout ensemble.
+narrateur|Le chien pose la tête, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15748,7 +16826,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Jules montre la poule. Papa a vu la dînette. Et un morceau de pain. Ça sent le pain chaud. Jules pose sa tête un moment. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>La poule picore près du bac, dehors. Ses plumes sont rousses, un peu mouillées. Elle fait cot cot, tout bas. On la regarde, tout doux. Nino s'accroupit, sans un mot. Raphaël attend à côté. Je lui tends le seau de grains. Nino pose le seau, tout lentement. On peut attendre. On peut tendre un jouet. On ne force pas la parole. On peut jouer ensemble. Bravo, Raphaël. Tu as tendu, sans presser. Une plume rousse reste sur la petite assiette. Raphaël a encore la dînette. Il reste une croûte de pain. On peut attendre. On peut tendre un jouet. J'ai attendu. Bravo. On ne force pas la parole.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15888,7 +16966,28 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Jules montre la poule. Papa a vu la dînette. Et un morceau de pain. Ça sent le pain chaud. Jules pose sa tête un moment. On peut attendre. On peut tendre un jouet. Pas forcer la parole. On peut attendre. On peut tendre un jouet. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près du bac, dehors.
+narrateur|Ses plumes sont rousses, un peu mouillées.
+narrateur|Elle fait cot cot, tout bas.
+maman|On la regarde, tout doux.
+narrateur|Nino s'accroupit, sans un mot.
+narrateur|Raphaël attend à côté.
+enfant-m|Je lui tends le seau de grains.
+narrateur|Nino pose le seau, tout lentement.
+papa|On peut attendre.
+papa|On peut tendre un jouet.
+maman|On ne force pas la parole.
+maman|On peut jouer ensemble.
+papa|Bravo, Raphaël.
+papa|Tu as tendu, sans presser.
+narrateur|Une plume rousse reste sur la petite assiette.
+narrateur|Raphaël a encore la dînette.
+narrateur|Il reste une croûte de pain.
+maman|On peut attendre.
+papa|On peut tendre un jouet.
+enfant-m|J'ai attendu.
+maman|Bravo.
+papa|On ne force pas la parole.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15916,7 +17015,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, papa. Merci, maman. Bravo, Raphaël. Tu as fait du bon travail. Tu as su attendre. Raphaël a joué avec la dînette. Nino a pris le pain, sans parler. Ils ont vu la poule, tout ensemble. La poule rentre sous l'auvent, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16056,7 +17155,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as su attendre.
+narrateur|Raphaël a joué avec la dînette.
+narrateur|Nino a pris le pain, sans parler.
+narrateur|Ils ont vu la poule, tout ensemble.
+narrateur|La poule rentre sous l'auvent, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16078,7 +17186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16116,6 +17224,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
